--- a/data/trans_dic/P16A01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A01-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,26</t>
+          <t>3,95; 7,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,69</t>
+          <t>7,97; 12,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,93</t>
+          <t>4,21; 7,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,9</t>
+          <t>4,38; 8,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,63</t>
+          <t>2,85; 5,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 11,06</t>
+          <t>6,55; 11,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,87</t>
+          <t>6,62; 10,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,05</t>
+          <t>4,96; 8,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 6,08</t>
+          <t>3,68; 5,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 10,98</t>
+          <t>7,81; 10,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,67</t>
+          <t>5,82; 8,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,39</t>
+          <t>5,13; 7,44</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,74</t>
+          <t>6,02; 9,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,18</t>
+          <t>5,8; 9,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,51</t>
+          <t>6,83; 10,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,65</t>
+          <t>2,74; 8,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,74</t>
+          <t>4,65; 7,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,51</t>
+          <t>6,02; 9,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,19</t>
+          <t>6,6; 10,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 10,92</t>
+          <t>7,42; 10,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 8,26</t>
+          <t>5,68; 8,12</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,7</t>
+          <t>6,43; 8,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,7</t>
+          <t>7,24; 9,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,98</t>
+          <t>4,8; 8,79</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,41</t>
+          <t>5,18; 9,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,75</t>
+          <t>8,84; 14,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,82</t>
+          <t>5,18; 8,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,98</t>
+          <t>4,82; 9,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 8,52</t>
+          <t>4,88; 8,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,01; 9,88</t>
+          <t>5,98; 9,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 8,91</t>
+          <t>5,28; 9,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,31</t>
+          <t>2,01; 6,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 8,29</t>
+          <t>5,49; 8,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 10,93</t>
+          <t>7,89; 10,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,25</t>
+          <t>5,64; 8,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,66</t>
+          <t>3,35; 6,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,93</t>
+          <t>5,79; 8,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,47</t>
+          <t>8,1; 12,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,85</t>
+          <t>7,27; 11,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,26</t>
+          <t>5,91; 10,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,01</t>
+          <t>6,76; 10,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,13</t>
+          <t>7,41; 11,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,26</t>
+          <t>7,49; 11,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,0</t>
+          <t>6,43; 9,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 8,95</t>
+          <t>6,63; 9,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,34; 11,06</t>
+          <t>8,46; 11,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,85; 10,41</t>
+          <t>7,93; 10,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 9,46</t>
+          <t>6,84; 9,57</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,81</t>
+          <t>6,07; 7,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 10,67</t>
+          <t>8,38; 10,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,73</t>
+          <t>6,76; 8,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 7,67</t>
+          <t>5,08; 7,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,35</t>
+          <t>5,6; 7,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 9,31</t>
+          <t>7,42; 9,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,28</t>
+          <t>7,37; 9,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,12</t>
+          <t>5,86; 8,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,37</t>
+          <t>6,02; 7,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 9,58</t>
+          <t>8,14; 9,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 8,66</t>
+          <t>7,35; 8,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,73</t>
+          <t>5,96; 7,71</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26609; 50307</t>
+          <t>27384; 51091</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55275; 88945</t>
+          <t>55853; 88819</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28882; 53491</t>
+          <t>28403; 53510</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26621; 50184</t>
+          <t>27819; 51026</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19209; 38765</t>
+          <t>19643; 39654</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45925; 76676</t>
+          <t>45416; 76301</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43476; 73113</t>
+          <t>44515; 72979</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33458; 54387</t>
+          <t>33488; 54364</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50257; 83979</t>
+          <t>50859; 82054</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>107540; 153101</t>
+          <t>108869; 152626</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78973; 116850</t>
+          <t>78374; 117278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>66054; 96894</t>
+          <t>67184; 97523</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59517; 93710</t>
+          <t>57923; 95088</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58465; 93496</t>
+          <t>59081; 93293</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69524; 107505</t>
+          <t>69784; 106611</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35048; 103219</t>
+          <t>32729; 101489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44103; 75002</t>
+          <t>44987; 76834</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62353; 97656</t>
+          <t>61803; 96461</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67767; 106265</t>
+          <t>68789; 105618</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72253; 104632</t>
+          <t>71050; 103396</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>112860; 159455</t>
+          <t>109694; 156652</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>129030; 177790</t>
+          <t>131415; 179959</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>146153; 200274</t>
+          <t>149462; 200383</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>108225; 193139</t>
+          <t>103161; 188967</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34871; 63867</t>
+          <t>35166; 64448</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67269; 104027</t>
+          <t>66914; 107149</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38554; 67014</t>
+          <t>39359; 67902</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32530; 63218</t>
+          <t>33901; 64021</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33180; 58256</t>
+          <t>33356; 59508</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46616; 76664</t>
+          <t>46439; 77401</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41335; 69953</t>
+          <t>41453; 70988</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19968; 58824</t>
+          <t>18760; 61344</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>74046; 112880</t>
+          <t>74839; 111244</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121039; 167504</t>
+          <t>120902; 167766</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86625; 127387</t>
+          <t>87074; 128275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>56467; 108879</t>
+          <t>54720; 111305</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53142; 84159</t>
+          <t>54547; 83925</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76082; 117753</t>
+          <t>76492; 116622</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67568; 101767</t>
+          <t>68183; 103318</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56884; 95084</t>
+          <t>54781; 94218</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>69673; 103927</t>
+          <t>70230; 105883</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>79085; 116682</t>
+          <t>77748; 116824</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78359; 117544</t>
+          <t>78132; 116988</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70723; 109096</t>
+          <t>70125; 107395</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>132045; 177233</t>
+          <t>131387; 180893</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166206; 220487</t>
+          <t>168597; 222316</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>155583; 206169</t>
+          <t>157094; 206854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>137159; 190836</t>
+          <t>137980; 193129</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>196981; 255794</t>
+          <t>198803; 256265</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>289602; 364737</t>
+          <t>286616; 357926</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>230616; 296394</t>
+          <t>229355; 294465</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>174870; 265333</t>
+          <t>175822; 267910</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>187296; 248215</t>
+          <t>189238; 247559</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>265277; 330185</t>
+          <t>262955; 336776</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>261087; 328950</t>
+          <t>261307; 330404</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>211773; 296798</t>
+          <t>214202; 295894</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>405507; 490355</t>
+          <t>400407; 487562</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>568021; 667252</t>
+          <t>566712; 667732</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>508103; 600878</t>
+          <t>510177; 605538</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>428685; 549704</t>
+          <t>424323; 548369</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A01-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A01-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,37</t>
+          <t>3,86; 7,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 12,67</t>
+          <t>7,86; 12,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,93</t>
+          <t>4,24; 7,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,03</t>
+          <t>4,33; 8,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,76</t>
+          <t>2,81; 5,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,0</t>
+          <t>6,84; 10,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,85</t>
+          <t>6,45; 10,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,05</t>
+          <t>5,0; 7,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 5,94</t>
+          <t>3,68; 5,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 10,95</t>
+          <t>7,72; 10,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,7</t>
+          <t>5,93; 8,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 7,44</t>
+          <t>5,17; 7,45</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,89</t>
+          <t>6,13; 9,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,16</t>
+          <t>5,66; 9,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 10,43</t>
+          <t>6,73; 10,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,51</t>
+          <t>5,72; 9,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,93</t>
+          <t>4,61; 7,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,4</t>
+          <t>6,09; 9,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 10,13</t>
+          <t>6,65; 10,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 10,79</t>
+          <t>7,03; 10,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,12</t>
+          <t>5,82; 8,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 8,8</t>
+          <t>6,4; 8,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,7</t>
+          <t>7,24; 9,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,79</t>
+          <t>6,98; 9,57</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 9,5</t>
+          <t>5,24; 9,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,84; 14,16</t>
+          <t>8,9; 13,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,94</t>
+          <t>5,04; 8,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 9,1</t>
+          <t>4,79; 8,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,7</t>
+          <t>4,72; 8,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 9,97</t>
+          <t>5,97; 9,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,04</t>
+          <t>5,21; 9,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,58</t>
+          <t>4,73; 8,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,49; 8,17</t>
+          <t>5,59; 8,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,89; 10,94</t>
+          <t>7,84; 10,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 8,3</t>
+          <t>5,57; 8,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,8</t>
+          <t>5,11; 7,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,91</t>
+          <t>5,83; 9,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 12,35</t>
+          <t>8,19; 12,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 11,02</t>
+          <t>7,02; 10,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,17</t>
+          <t>6,44; 10,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,19</t>
+          <t>6,61; 10,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 11,14</t>
+          <t>7,43; 11,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 11,21</t>
+          <t>7,37; 11,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,84</t>
+          <t>7,45; 10,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 9,13</t>
+          <t>6,63; 9,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 11,16</t>
+          <t>8,33; 11,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 10,44</t>
+          <t>7,84; 10,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 9,57</t>
+          <t>7,41; 9,75</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,82</t>
+          <t>6,11; 7,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,47</t>
+          <t>8,38; 10,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,68</t>
+          <t>6,81; 8,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,75</t>
+          <t>6,27; 8,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,6; 7,33</t>
+          <t>5,65; 7,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,5</t>
+          <t>7,3; 9,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,32</t>
+          <t>7,4; 9,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,09</t>
+          <t>6,98; 8,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,33</t>
+          <t>6,1; 7,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 9,59</t>
+          <t>8,17; 9,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,73</t>
+          <t>7,4; 8,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,71</t>
+          <t>6,89; 8,12</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37584</t>
+          <t>40710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>47102</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>80771</t>
+          <t>87812</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27384; 51091</t>
+          <t>26747; 52023</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55853; 88819</t>
+          <t>55050; 87027</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28403; 53510</t>
+          <t>28611; 53708</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27819; 51026</t>
+          <t>29890; 55452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19643; 39654</t>
+          <t>19340; 40735</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45416; 76301</t>
+          <t>47446; 75460</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44515; 72979</t>
+          <t>43379; 72667</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33488; 54364</t>
+          <t>36653; 57940</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50859; 82054</t>
+          <t>50898; 80815</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>108869; 152626</t>
+          <t>107605; 151256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78374; 117278</t>
+          <t>79894; 117222</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>67184; 97523</t>
+          <t>73579; 106036</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72922</t>
+          <t>80082</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>85744</t>
+          <t>92017</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>158666</t>
+          <t>172098</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57923; 95088</t>
+          <t>58969; 93775</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59081; 93293</t>
+          <t>57621; 94236</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69784; 106611</t>
+          <t>68834; 106135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32729; 101489</t>
+          <t>59952; 101618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44987; 76834</t>
+          <t>44617; 76069</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61803; 96461</t>
+          <t>62570; 97534</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68789; 105618</t>
+          <t>69371; 105302</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71050; 103396</t>
+          <t>75279; 110648</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>109694; 156652</t>
+          <t>112431; 157274</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131415; 179959</t>
+          <t>130944; 180447</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>149462; 200383</t>
+          <t>149428; 202718</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>103161; 188967</t>
+          <t>147878; 202879</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45646</t>
+          <t>51171</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41946</t>
+          <t>50922</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87592</t>
+          <t>102093</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35166; 64448</t>
+          <t>35565; 64090</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66914; 107149</t>
+          <t>67329; 104421</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39359; 67902</t>
+          <t>38289; 66338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33901; 64021</t>
+          <t>38460; 70235</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33356; 59508</t>
+          <t>32271; 56953</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46439; 77401</t>
+          <t>46319; 76289</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41453; 70988</t>
+          <t>40866; 70855</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18760; 61344</t>
+          <t>38382; 65322</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>74839; 111244</t>
+          <t>76158; 113777</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120902; 167766</t>
+          <t>120161; 167980</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87074; 128275</t>
+          <t>86100; 127396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54720; 111305</t>
+          <t>82376; 125264</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72479</t>
+          <t>81707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90615</t>
+          <t>98282</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>163094</t>
+          <t>179989</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>54547; 83925</t>
+          <t>54944; 84763</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76492; 116622</t>
+          <t>77316; 117332</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68183; 103318</t>
+          <t>65818; 100152</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54781; 94218</t>
+          <t>63734; 104478</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70230; 105883</t>
+          <t>68698; 103853</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77748; 116824</t>
+          <t>77889; 115424</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>78132; 116988</t>
+          <t>76916; 117022</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70125; 107395</t>
+          <t>83179; 115461</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>131387; 180893</t>
+          <t>131259; 179276</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>168597; 222316</t>
+          <t>165919; 221138</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>157094; 206854</t>
+          <t>155290; 207581</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>137980; 193129</t>
+          <t>156064; 205503</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>228631</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>261492</t>
+          <t>288323</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>490123</t>
+          <t>541992</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>198803; 256265</t>
+          <t>200192; 258625</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>286616; 357926</t>
+          <t>286621; 359400</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>229355; 294465</t>
+          <t>231227; 294228</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>175822; 267910</t>
+          <t>221574; 293991</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>189238; 247559</t>
+          <t>190866; 247570</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>262955; 336776</t>
+          <t>258865; 330169</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>261307; 330404</t>
+          <t>262304; 330691</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>214202; 295894</t>
+          <t>260374; 318892</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>400407; 487562</t>
+          <t>405828; 486224</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>566712; 667732</t>
+          <t>569144; 671198</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>510177; 605538</t>
+          <t>513221; 608988</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>424323; 548369</t>
+          <t>500101; 589879</t>
         </is>
       </c>
     </row>
